--- a/Data/4DataSet_PLM.xlsx
+++ b/Data/4DataSet_PLM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\##Paper2\数据整理\OT_QCM2Net\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niu\Documents\Codex\2026-07-14\7-30-slack-plugin-slack-openai-4\outputs\VLM_DTI_FinalProvenance_20260723\VLM-DTI source code\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A5208A-6047-4D33-AC8B-4CEB9C5C0845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9931CD-8D04-4A5A-9944-950770901C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="645" windowWidth="13995" windowHeight="14550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="810" windowWidth="16350" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="celegans" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="19">
   <si>
     <t>Dataset</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Seed</t>
-  </si>
-  <si>
-    <t>BestEpoch</t>
   </si>
   <si>
     <t>AUC_Test</t>
@@ -108,18 +105,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -127,7 +124,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -135,7 +132,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -143,7 +140,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -151,7 +148,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -159,7 +156,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -167,7 +164,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -175,7 +172,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -183,7 +180,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线 Light"/>
+      <name val="Yu Gothic Light"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -192,7 +189,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -201,7 +198,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -210,7 +207,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -218,7 +215,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -226,7 +223,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -234,7 +231,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -242,7 +239,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -251,7 +248,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -260,7 +257,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -268,7 +265,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -277,7 +274,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -285,7 +282,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -294,7 +291,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -303,7 +300,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -311,14 +308,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1486,13 +1483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,1047 +1520,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>23</v>
+        <v>0.99209999999999998</v>
       </c>
       <c r="E2" s="4">
-        <v>0.99209999999999998</v>
+        <v>0.99119999999999997</v>
       </c>
       <c r="F2" s="4">
         <v>0.99119999999999997</v>
       </c>
       <c r="G2" s="4">
-        <v>0.99119999999999997</v>
+        <v>0.94550000000000001</v>
       </c>
       <c r="H2" s="4">
-        <v>0.94550000000000001</v>
+        <v>0.97070000000000001</v>
       </c>
       <c r="I2" s="4">
-        <v>0.97070000000000001</v>
+        <v>0.95889999999999997</v>
       </c>
       <c r="J2" s="4">
-        <v>0.95889999999999997</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.95789999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>29</v>
+        <v>0.99380000000000002</v>
       </c>
       <c r="E3" s="4">
-        <v>0.99380000000000002</v>
+        <v>0.99390000000000001</v>
       </c>
       <c r="F3" s="4">
         <v>0.99390000000000001</v>
       </c>
       <c r="G3" s="4">
-        <v>0.99390000000000001</v>
+        <v>0.9556</v>
       </c>
       <c r="H3" s="4">
-        <v>0.9556</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I3" s="4">
-        <v>0.97599999999999998</v>
+        <v>0.96660000000000001</v>
       </c>
       <c r="J3" s="4">
-        <v>0.96660000000000001</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.9657</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>30</v>
+        <v>0.99429999999999996</v>
       </c>
       <c r="E4" s="4">
-        <v>0.99429999999999996</v>
+        <v>0.99419999999999997</v>
       </c>
       <c r="F4" s="4">
         <v>0.99419999999999997</v>
       </c>
       <c r="G4" s="4">
-        <v>0.99419999999999997</v>
+        <v>0.95530000000000004</v>
       </c>
       <c r="H4" s="4">
-        <v>0.95530000000000004</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="I4" s="4">
-        <v>0.96799999999999997</v>
+        <v>0.96279999999999999</v>
       </c>
       <c r="J4" s="4">
-        <v>0.96279999999999999</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.96160000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>27</v>
+        <v>0.99239999999999995</v>
       </c>
       <c r="E5" s="4">
-        <v>0.99239999999999995</v>
+        <v>0.99319999999999997</v>
       </c>
       <c r="F5" s="4">
         <v>0.99319999999999997</v>
       </c>
       <c r="G5" s="4">
-        <v>0.99319999999999997</v>
+        <v>0.93379999999999996</v>
       </c>
       <c r="H5" s="4">
-        <v>0.93379999999999996</v>
+        <v>0.97870000000000001</v>
       </c>
       <c r="I5" s="4">
-        <v>0.97870000000000001</v>
+        <v>0.95640000000000003</v>
       </c>
       <c r="J5" s="4">
-        <v>0.95640000000000003</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.95569999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>21</v>
+        <v>0.99370000000000003</v>
       </c>
       <c r="E6" s="4">
-        <v>0.99370000000000003</v>
+        <v>0.99380000000000002</v>
       </c>
       <c r="F6" s="4">
         <v>0.99380000000000002</v>
       </c>
       <c r="G6" s="4">
-        <v>0.99380000000000002</v>
+        <v>0.96030000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>0.96030000000000004</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="I6" s="4">
-        <v>0.96799999999999997</v>
+        <v>0.96530000000000005</v>
       </c>
       <c r="J6" s="4">
-        <v>0.96530000000000005</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.96409999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9933±0.0010</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9933±0.0010</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9933±0.0012</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9933±0.0012</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9933±0.0012</v>
+        <v>0.9501±0.0106</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9501±0.0106</v>
+        <v>0.9723±0.0049</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9723±0.0049</v>
+        <v>0.9620±0.0043</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9620±0.0043</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9610±0.0042</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>22</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="E8" s="4">
-        <v>0.92700000000000005</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="F8" s="4">
-        <v>0.90600000000000003</v>
+        <v>0.90610000000000002</v>
       </c>
       <c r="G8" s="4">
-        <v>0.90610000000000002</v>
+        <v>0.81569999999999998</v>
       </c>
       <c r="H8" s="4">
-        <v>0.81569999999999998</v>
+        <v>0.82950000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>0.82950000000000002</v>
+        <v>0.85050000000000003</v>
       </c>
       <c r="J8" s="4">
-        <v>0.85050000000000003</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.82250000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>13</v>
+        <v>0.93440000000000001</v>
       </c>
       <c r="E9" s="4">
-        <v>0.93440000000000001</v>
+        <v>0.91080000000000005</v>
       </c>
       <c r="F9" s="4">
-        <v>0.91080000000000005</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="G9" s="4">
-        <v>0.91100000000000003</v>
+        <v>0.82420000000000004</v>
       </c>
       <c r="H9" s="4">
-        <v>0.82420000000000004</v>
+        <v>0.81889999999999996</v>
       </c>
       <c r="I9" s="4">
-        <v>0.81889999999999996</v>
+        <v>0.85140000000000005</v>
       </c>
       <c r="J9" s="4">
-        <v>0.85140000000000005</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.82150000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>15</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="E10" s="4">
-        <v>0.92300000000000004</v>
+        <v>0.86270000000000002</v>
       </c>
       <c r="F10" s="4">
-        <v>0.86270000000000002</v>
+        <v>0.86319999999999997</v>
       </c>
       <c r="G10" s="4">
-        <v>0.86319999999999997</v>
+        <v>0.73970000000000002</v>
       </c>
       <c r="H10" s="4">
-        <v>0.73970000000000002</v>
+        <v>0.9032</v>
       </c>
       <c r="I10" s="4">
-        <v>0.9032</v>
+        <v>0.82669999999999999</v>
       </c>
       <c r="J10" s="4">
-        <v>0.82669999999999999</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.81330000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>30</v>
+        <v>0.94979999999999998</v>
       </c>
       <c r="E11" s="4">
-        <v>0.94979999999999998</v>
+        <v>0.93789999999999996</v>
       </c>
       <c r="F11" s="4">
         <v>0.93789999999999996</v>
       </c>
       <c r="G11" s="4">
-        <v>0.93789999999999996</v>
+        <v>0.8649</v>
       </c>
       <c r="H11" s="4">
-        <v>0.8649</v>
+        <v>0.87580000000000002</v>
       </c>
       <c r="I11" s="4">
-        <v>0.87580000000000002</v>
+        <v>0.89090000000000003</v>
       </c>
       <c r="J11" s="4">
-        <v>0.89090000000000003</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.87029999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>18</v>
+        <v>0.92889999999999995</v>
       </c>
       <c r="E12" s="4">
-        <v>0.92889999999999995</v>
+        <v>0.90310000000000001</v>
       </c>
       <c r="F12" s="4">
-        <v>0.90310000000000001</v>
+        <v>0.90329999999999999</v>
       </c>
       <c r="G12" s="4">
-        <v>0.90329999999999999</v>
+        <v>0.80520000000000003</v>
       </c>
       <c r="H12" s="4">
-        <v>0.80520000000000003</v>
+        <v>0.85260000000000002</v>
       </c>
       <c r="I12" s="4">
-        <v>0.85260000000000002</v>
+        <v>0.85219999999999996</v>
       </c>
       <c r="J12" s="4">
-        <v>0.85219999999999996</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.82820000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9326±0.0104</v>
+      </c>
       <c r="E13" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9326±0.0104</v>
+        <f t="shared" ref="E13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
+        <v>0.9041±0.0270</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" ref="F13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(F8:F12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F8:F12),"0.0000")</f>
-        <v>0.9041±0.0270</v>
+        <f t="shared" si="1"/>
+        <v>0.9043±0.0268</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9043±0.0268</v>
+        <v>0.8099±0.0453</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8099±0.0453</v>
+        <v>0.8560±0.0343</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8560±0.0343</v>
+        <v>0.8543±0.0231</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8543±0.0231</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8312±0.0225</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>29</v>
+        <v>0.97719999999999996</v>
       </c>
       <c r="E14" s="4">
-        <v>0.97719999999999996</v>
+        <v>0.98240000000000005</v>
       </c>
       <c r="F14" s="4">
         <v>0.98240000000000005</v>
       </c>
       <c r="G14" s="4">
-        <v>0.98240000000000005</v>
+        <v>0.9718</v>
       </c>
       <c r="H14" s="4">
-        <v>0.9718</v>
+        <v>0.89680000000000004</v>
       </c>
       <c r="I14" s="4">
-        <v>0.89680000000000004</v>
+        <v>0.92630000000000001</v>
       </c>
       <c r="J14" s="4">
-        <v>0.92630000000000001</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.93279999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>8</v>
+        <v>0.96950000000000003</v>
       </c>
       <c r="E15" s="4">
-        <v>0.96950000000000003</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="F15" s="4">
         <v>0.97699999999999998</v>
       </c>
       <c r="G15" s="4">
-        <v>0.97699999999999998</v>
+        <v>0.97089999999999999</v>
       </c>
       <c r="H15" s="4">
-        <v>0.97089999999999999</v>
+        <v>0.80669999999999997</v>
       </c>
       <c r="I15" s="4">
-        <v>0.80669999999999997</v>
+        <v>0.87590000000000001</v>
       </c>
       <c r="J15" s="4">
-        <v>0.87590000000000001</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.88119999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>6</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="E16" s="4">
-        <v>0.97499999999999998</v>
+        <v>0.98</v>
       </c>
       <c r="F16" s="4">
         <v>0.98</v>
       </c>
       <c r="G16" s="4">
-        <v>0.98</v>
+        <v>0.96709999999999996</v>
       </c>
       <c r="H16" s="4">
-        <v>0.96709999999999996</v>
+        <v>0.87549999999999994</v>
       </c>
       <c r="I16" s="4">
-        <v>0.87549999999999994</v>
+        <v>0.91190000000000004</v>
       </c>
       <c r="J16" s="4">
-        <v>0.91190000000000004</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.91900000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>19</v>
+        <v>0.9627</v>
       </c>
       <c r="E17" s="4">
-        <v>0.9627</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="F17" s="4">
         <v>0.97199999999999998</v>
       </c>
       <c r="G17" s="4">
-        <v>0.97199999999999998</v>
+        <v>0.96679999999999999</v>
       </c>
       <c r="H17" s="4">
-        <v>0.96679999999999999</v>
+        <v>0.84009999999999996</v>
       </c>
       <c r="I17" s="4">
-        <v>0.84009999999999996</v>
+        <v>0.89229999999999998</v>
       </c>
       <c r="J17" s="4">
-        <v>0.89229999999999998</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.89910000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>17</v>
+        <v>0.9647</v>
       </c>
       <c r="E18" s="4">
-        <v>0.9647</v>
+        <v>0.97189999999999999</v>
       </c>
       <c r="F18" s="4">
         <v>0.97189999999999999</v>
       </c>
       <c r="G18" s="4">
-        <v>0.97189999999999999</v>
+        <v>0.95760000000000001</v>
       </c>
       <c r="H18" s="4">
-        <v>0.95760000000000001</v>
+        <v>0.81779999999999997</v>
       </c>
       <c r="I18" s="4">
-        <v>0.81779999999999997</v>
+        <v>0.87529999999999997</v>
       </c>
       <c r="J18" s="4">
-        <v>0.87529999999999997</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.88219999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9698±0.0063</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9698±0.0063</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9767±0.0047</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
+        <f t="shared" si="2"/>
         <v>0.9767±0.0047</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9767±0.0047</v>
+        <v>0.9668±0.0056</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9668±0.0056</v>
+        <v>0.8474±0.0381</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8474±0.0381</v>
+        <v>0.8963±0.0225</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8963±0.0225</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.9029±0.0227</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>21</v>
+        <v>0.99490000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>0.99490000000000001</v>
+        <v>0.99550000000000005</v>
       </c>
       <c r="F20" s="4">
         <v>0.99550000000000005</v>
       </c>
       <c r="G20" s="4">
-        <v>0.99550000000000005</v>
+        <v>0.95420000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>0.95420000000000005</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="I20" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="J20" s="4">
-        <v>0.96579999999999999</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.96689999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>20</v>
+        <v>0.99490000000000001</v>
       </c>
       <c r="E21" s="4">
-        <v>0.99490000000000001</v>
+        <v>0.99590000000000001</v>
       </c>
       <c r="F21" s="4">
         <v>0.99590000000000001</v>
       </c>
       <c r="G21" s="4">
-        <v>0.99590000000000001</v>
+        <v>0.96050000000000002</v>
       </c>
       <c r="H21" s="4">
-        <v>0.96050000000000002</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="I21" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.96919999999999995</v>
       </c>
       <c r="J21" s="4">
-        <v>0.96919999999999995</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.97009999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>24</v>
+        <v>0.99370000000000003</v>
       </c>
       <c r="E22" s="4">
-        <v>0.99370000000000003</v>
+        <v>0.99460000000000004</v>
       </c>
       <c r="F22" s="4">
         <v>0.99460000000000004</v>
       </c>
       <c r="G22" s="4">
-        <v>0.99460000000000004</v>
+        <v>0.94740000000000002</v>
       </c>
       <c r="H22" s="4">
-        <v>0.94740000000000002</v>
+        <v>0.96640000000000004</v>
       </c>
       <c r="I22" s="4">
-        <v>0.96640000000000004</v>
+        <v>0.95550000000000002</v>
       </c>
       <c r="J22" s="4">
-        <v>0.95550000000000002</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.95679999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>9</v>
+        <v>0.9859</v>
       </c>
       <c r="E23" s="4">
-        <v>0.9859</v>
+        <v>0.98729999999999996</v>
       </c>
       <c r="F23" s="4">
         <v>0.98729999999999996</v>
       </c>
       <c r="G23" s="4">
-        <v>0.98729999999999996</v>
+        <v>0.9536</v>
       </c>
       <c r="H23" s="4">
-        <v>0.9536</v>
+        <v>0.96640000000000004</v>
       </c>
       <c r="I23" s="4">
-        <v>0.96640000000000004</v>
+        <v>0.95889999999999997</v>
       </c>
       <c r="J23" s="4">
-        <v>0.95889999999999997</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.96</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>23</v>
+        <v>0.99270000000000003</v>
       </c>
       <c r="E24" s="4">
-        <v>0.99270000000000003</v>
+        <v>0.99319999999999997</v>
       </c>
       <c r="F24" s="4">
         <v>0.99319999999999997</v>
       </c>
       <c r="G24" s="4">
-        <v>0.99319999999999997</v>
+        <v>0.94810000000000005</v>
       </c>
       <c r="H24" s="4">
-        <v>0.94810000000000005</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="I24" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.96230000000000004</v>
       </c>
       <c r="J24" s="4">
-        <v>0.96230000000000004</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.9637</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9924±0.0038</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9924±0.0038</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9933±0.0035</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
+        <f t="shared" si="3"/>
         <v>0.9933±0.0035</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9933±0.0035</v>
+        <v>0.9528±0.0053</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9528±0.0053</v>
+        <v>0.9745±0.0074</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9745±0.0074</v>
+        <v>0.9623±0.0054</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9623±0.0054</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.9635±0.0053</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>24</v>
+        <v>0.99070000000000003</v>
       </c>
       <c r="E26" s="4">
-        <v>0.99070000000000003</v>
+        <v>0.99409999999999998</v>
       </c>
       <c r="F26" s="4">
         <v>0.99409999999999998</v>
       </c>
       <c r="G26" s="4">
-        <v>0.99409999999999998</v>
+        <v>0.98509999999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>0.98509999999999998</v>
+        <v>0.9496</v>
       </c>
       <c r="I26" s="4">
-        <v>0.9496</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="J26" s="4">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.96699999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>28</v>
+        <v>0.99790000000000001</v>
       </c>
       <c r="E27" s="4">
-        <v>0.99790000000000001</v>
+        <v>0.99839999999999995</v>
       </c>
       <c r="F27" s="4">
         <v>0.99839999999999995</v>
       </c>
       <c r="G27" s="4">
-        <v>0.99839999999999995</v>
+        <v>0.99260000000000004</v>
       </c>
       <c r="H27" s="4">
-        <v>0.99260000000000004</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="I27" s="4">
-        <v>0.96399999999999997</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J27" s="4">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>26</v>
+        <v>0.996</v>
       </c>
       <c r="E28" s="4">
-        <v>0.996</v>
+        <v>0.99680000000000002</v>
       </c>
       <c r="F28" s="4">
         <v>0.99680000000000002</v>
       </c>
       <c r="G28" s="4">
-        <v>0.99680000000000002</v>
+        <v>0.97119999999999995</v>
       </c>
       <c r="H28" s="4">
         <v>0.97119999999999995</v>
       </c>
       <c r="I28" s="4">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="J28" s="4">
         <v>0.97119999999999995</v>
       </c>
-      <c r="J28" s="4">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="K28" s="4">
-        <v>0.97119999999999995</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>28</v>
+        <v>0.99590000000000001</v>
       </c>
       <c r="E29" s="4">
-        <v>0.99590000000000001</v>
+        <v>0.99719999999999998</v>
       </c>
       <c r="F29" s="4">
         <v>0.99719999999999998</v>
       </c>
       <c r="G29" s="4">
-        <v>0.99719999999999998</v>
+        <v>0.97860000000000003</v>
       </c>
       <c r="H29" s="4">
-        <v>0.97860000000000003</v>
+        <v>0.98560000000000003</v>
       </c>
       <c r="I29" s="4">
-        <v>0.98560000000000003</v>
+        <v>0.98</v>
       </c>
       <c r="J29" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.98209999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>25</v>
+        <v>0.99639999999999995</v>
       </c>
       <c r="E30" s="4">
-        <v>0.99639999999999995</v>
+        <v>0.99750000000000005</v>
       </c>
       <c r="F30" s="4">
         <v>0.99750000000000005</v>
       </c>
       <c r="G30" s="4">
-        <v>0.99750000000000005</v>
+        <v>0.98519999999999996</v>
       </c>
       <c r="H30" s="4">
-        <v>0.98519999999999996</v>
+        <v>0.95679999999999998</v>
       </c>
       <c r="I30" s="4">
-        <v>0.95679999999999998</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="J30" s="4">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.9708</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9954±0.0027</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9954±0.0027</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9968±0.0016</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
+        <f t="shared" si="4"/>
         <v>0.9968±0.0016</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9968±0.0016</v>
+        <v>0.9825±0.0080</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9825±0.0080</v>
+        <v>0.9654±0.0138</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9654±0.0138</v>
+        <v>0.9712±0.0066</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9712±0.0066</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9738±0.0061</v>
       </c>
@@ -2577,10 +2492,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4FE8A1-466E-4044-9083-70D3ABB3121B}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2611,1047 +2526,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>24</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="E2" s="4">
-        <v>0.98299999999999998</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="F2" s="4">
-        <v>0.98660000000000003</v>
+        <v>0.98670000000000002</v>
       </c>
       <c r="G2" s="4">
-        <v>0.98670000000000002</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="H2" s="4">
-        <v>0.94599999999999995</v>
+        <v>0.95689999999999997</v>
       </c>
       <c r="I2" s="4">
-        <v>0.95689999999999997</v>
+        <v>0.94950000000000001</v>
       </c>
       <c r="J2" s="4">
-        <v>0.94950000000000001</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.95140000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>23</v>
+        <v>0.98170000000000002</v>
       </c>
       <c r="E3" s="4">
-        <v>0.98170000000000002</v>
+        <v>0.98519999999999996</v>
       </c>
       <c r="F3" s="4">
         <v>0.98519999999999996</v>
       </c>
       <c r="G3" s="4">
-        <v>0.98519999999999996</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="H3" s="4">
-        <v>0.93200000000000005</v>
+        <v>0.94540000000000002</v>
       </c>
       <c r="I3" s="4">
-        <v>0.94540000000000002</v>
+        <v>0.93610000000000004</v>
       </c>
       <c r="J3" s="4">
-        <v>0.93610000000000004</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.93869999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>18</v>
+        <v>0.9869</v>
       </c>
       <c r="E4" s="4">
-        <v>0.9869</v>
+        <v>0.99009999999999998</v>
       </c>
       <c r="F4" s="4">
         <v>0.99009999999999998</v>
       </c>
       <c r="G4" s="4">
-        <v>0.99009999999999998</v>
+        <v>0.94889999999999997</v>
       </c>
       <c r="H4" s="4">
-        <v>0.94889999999999997</v>
+        <v>0.95979999999999999</v>
       </c>
       <c r="I4" s="4">
-        <v>0.95979999999999999</v>
+        <v>0.95250000000000001</v>
       </c>
       <c r="J4" s="4">
-        <v>0.95250000000000001</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.95430000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>26</v>
+        <v>0.98340000000000005</v>
       </c>
       <c r="E5" s="4">
-        <v>0.98340000000000005</v>
+        <v>0.98670000000000002</v>
       </c>
       <c r="F5" s="4">
         <v>0.98670000000000002</v>
       </c>
       <c r="G5" s="4">
-        <v>0.98670000000000002</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="H5" s="4">
-        <v>0.91300000000000003</v>
+        <v>0.96550000000000002</v>
       </c>
       <c r="I5" s="4">
-        <v>0.96550000000000002</v>
+        <v>0.93459999999999999</v>
       </c>
       <c r="J5" s="4">
-        <v>0.93459999999999999</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.9385</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>23</v>
+        <v>0.98329999999999995</v>
       </c>
       <c r="E6" s="4">
-        <v>0.98329999999999995</v>
+        <v>0.98839999999999995</v>
       </c>
       <c r="F6" s="4">
         <v>0.98839999999999995</v>
       </c>
       <c r="G6" s="4">
-        <v>0.98839999999999995</v>
+        <v>0.97070000000000001</v>
       </c>
       <c r="H6" s="4">
-        <v>0.97070000000000001</v>
+        <v>0.95109999999999995</v>
       </c>
       <c r="I6" s="4">
-        <v>0.95109999999999995</v>
+        <v>0.95989999999999998</v>
       </c>
       <c r="J6" s="4">
-        <v>0.95989999999999998</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.96079999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9837±0.0019</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9837±0.0019</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9874±0.0019</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9874±0.0019</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9874±0.0019</v>
+        <v>0.9421±0.0214</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9421±0.0214</v>
+        <v>0.9557±0.0078</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9557±0.0078</v>
+        <v>0.9465±0.0109</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9465±0.0109</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9487±0.0099</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>22</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="E8" s="4">
-        <v>0.90500000000000003</v>
+        <v>0.89910000000000001</v>
       </c>
       <c r="F8" s="4">
-        <v>0.89910000000000001</v>
+        <v>0.8992</v>
       </c>
       <c r="G8" s="4">
-        <v>0.8992</v>
+        <v>0.80320000000000003</v>
       </c>
       <c r="H8" s="4">
-        <v>0.80320000000000003</v>
+        <v>0.7893</v>
       </c>
       <c r="I8" s="4">
-        <v>0.7893</v>
+        <v>0.82410000000000005</v>
       </c>
       <c r="J8" s="4">
-        <v>0.82410000000000005</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.79620000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>16</v>
+        <v>0.88429999999999997</v>
       </c>
       <c r="E9" s="4">
-        <v>0.88429999999999997</v>
+        <v>0.88549999999999995</v>
       </c>
       <c r="F9" s="4">
         <v>0.88549999999999995</v>
       </c>
       <c r="G9" s="4">
-        <v>0.88549999999999995</v>
+        <v>0.80759999999999998</v>
       </c>
       <c r="H9" s="4">
-        <v>0.80759999999999998</v>
+        <v>0.77549999999999997</v>
       </c>
       <c r="I9" s="4">
-        <v>0.77549999999999997</v>
+        <v>0.82179999999999997</v>
       </c>
       <c r="J9" s="4">
-        <v>0.82179999999999997</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.79120000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>8</v>
+        <v>0.87870000000000004</v>
       </c>
       <c r="E10" s="4">
-        <v>0.87870000000000004</v>
+        <v>0.87529999999999997</v>
       </c>
       <c r="F10" s="4">
-        <v>0.87529999999999997</v>
+        <v>0.87539999999999996</v>
       </c>
       <c r="G10" s="4">
-        <v>0.87539999999999996</v>
+        <v>0.85129999999999995</v>
       </c>
       <c r="H10" s="4">
-        <v>0.85129999999999995</v>
+        <v>0.72189999999999999</v>
       </c>
       <c r="I10" s="4">
-        <v>0.72189999999999999</v>
+        <v>0.82410000000000005</v>
       </c>
       <c r="J10" s="4">
-        <v>0.82410000000000005</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.78129999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>22</v>
+        <v>0.90910000000000002</v>
       </c>
       <c r="E11" s="4">
-        <v>0.90910000000000002</v>
+        <v>0.89849999999999997</v>
       </c>
       <c r="F11" s="4">
-        <v>0.89849999999999997</v>
+        <v>0.89859999999999995</v>
       </c>
       <c r="G11" s="4">
-        <v>0.89859999999999995</v>
+        <v>0.79730000000000001</v>
       </c>
       <c r="H11" s="4">
-        <v>0.79730000000000001</v>
+        <v>0.81520000000000004</v>
       </c>
       <c r="I11" s="4">
-        <v>0.81520000000000004</v>
+        <v>0.82930000000000004</v>
       </c>
       <c r="J11" s="4">
-        <v>0.82930000000000004</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.80610000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>30</v>
+        <v>0.90590000000000004</v>
       </c>
       <c r="E12" s="4">
-        <v>0.90590000000000004</v>
+        <v>0.89759999999999995</v>
       </c>
       <c r="F12" s="4">
-        <v>0.89759999999999995</v>
+        <v>0.89770000000000005</v>
       </c>
       <c r="G12" s="4">
-        <v>0.89770000000000005</v>
+        <v>0.81469999999999998</v>
       </c>
       <c r="H12" s="4">
-        <v>0.81469999999999998</v>
+        <v>0.76680000000000004</v>
       </c>
       <c r="I12" s="4">
-        <v>0.76680000000000004</v>
+        <v>0.8226</v>
       </c>
       <c r="J12" s="4">
-        <v>0.8226</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.79</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.8966±0.0140</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.8966±0.0140</v>
+        <f t="shared" si="1"/>
+        <v>0.8912±0.0105</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8912±0.0105</v>
+        <v>0.8913±0.0105</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8913±0.0105</v>
+        <v>0.8148±0.0214</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8148±0.0214</v>
+        <v>0.7737±0.0343</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7737±0.0343</v>
+        <v>0.8244±0.0029</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8244±0.0029</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.7930±0.0091</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>22</v>
+        <v>0.97009999999999996</v>
       </c>
       <c r="E14" s="4">
-        <v>0.97009999999999996</v>
+        <v>0.95979999999999999</v>
       </c>
       <c r="F14" s="4">
-        <v>0.95979999999999999</v>
+        <v>0.95989999999999998</v>
       </c>
       <c r="G14" s="4">
-        <v>0.95989999999999998</v>
+        <v>0.90629999999999999</v>
       </c>
       <c r="H14" s="4">
-        <v>0.90629999999999999</v>
+        <v>0.90039999999999998</v>
       </c>
       <c r="I14" s="4">
-        <v>0.90039999999999998</v>
+        <v>0.92279999999999995</v>
       </c>
       <c r="J14" s="4">
-        <v>0.92279999999999995</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.90339999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>17</v>
+        <v>0.96909999999999996</v>
       </c>
       <c r="E15" s="4">
-        <v>0.96909999999999996</v>
+        <v>0.95850000000000002</v>
       </c>
       <c r="F15" s="4">
-        <v>0.95850000000000002</v>
+        <v>0.95860000000000001</v>
       </c>
       <c r="G15" s="4">
-        <v>0.95860000000000001</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="H15" s="4">
-        <v>0.88100000000000001</v>
+        <v>0.91339999999999999</v>
       </c>
       <c r="I15" s="4">
-        <v>0.91339999999999999</v>
+        <v>0.91590000000000005</v>
       </c>
       <c r="J15" s="4">
-        <v>0.91590000000000005</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.89690000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>28</v>
+        <v>0.97740000000000005</v>
       </c>
       <c r="E16" s="4">
-        <v>0.97740000000000005</v>
+        <v>0.96870000000000001</v>
       </c>
       <c r="F16" s="4">
-        <v>0.96870000000000001</v>
+        <v>0.96879999999999999</v>
       </c>
       <c r="G16" s="4">
-        <v>0.96879999999999999</v>
+        <v>0.90380000000000005</v>
       </c>
       <c r="H16" s="4">
-        <v>0.90380000000000005</v>
+        <v>0.93510000000000004</v>
       </c>
       <c r="I16" s="4">
-        <v>0.93510000000000004</v>
+        <v>0.93410000000000004</v>
       </c>
       <c r="J16" s="4">
-        <v>0.93410000000000004</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.91910000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>24</v>
+        <v>0.96130000000000004</v>
       </c>
       <c r="E17" s="4">
-        <v>0.96130000000000004</v>
+        <v>0.95050000000000001</v>
       </c>
       <c r="F17" s="4">
-        <v>0.95050000000000001</v>
+        <v>0.9506</v>
       </c>
       <c r="G17" s="4">
-        <v>0.9506</v>
+        <v>0.86529999999999996</v>
       </c>
       <c r="H17" s="4">
-        <v>0.86529999999999996</v>
+        <v>0.91769999999999996</v>
       </c>
       <c r="I17" s="4">
-        <v>0.91769999999999996</v>
+        <v>0.90980000000000005</v>
       </c>
       <c r="J17" s="4">
-        <v>0.90980000000000005</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.89080000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>29</v>
+        <v>0.96440000000000003</v>
       </c>
       <c r="E18" s="4">
-        <v>0.96440000000000003</v>
+        <v>0.95750000000000002</v>
       </c>
       <c r="F18" s="4">
         <v>0.95750000000000002</v>
       </c>
       <c r="G18" s="4">
-        <v>0.95750000000000002</v>
+        <v>0.92259999999999998</v>
       </c>
       <c r="H18" s="4">
-        <v>0.92259999999999998</v>
+        <v>0.87660000000000005</v>
       </c>
       <c r="I18" s="4">
-        <v>0.87660000000000005</v>
+        <v>0.92110000000000003</v>
       </c>
       <c r="J18" s="4">
-        <v>0.92110000000000003</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.89900000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9685±0.0061</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9685±0.0061</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9590±0.0065</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.9590±0.0065</v>
+        <f t="shared" si="2"/>
+        <v>0.9591±0.0065</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9591±0.0065</v>
+        <v>0.8958±0.0226</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8958±0.0226</v>
+        <v>0.9086±0.0218</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9086±0.0218</v>
+        <v>0.9207±0.0090</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9207±0.0090</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.9018±0.0107</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>17</v>
+        <v>0.97309999999999997</v>
       </c>
       <c r="E20" s="4">
-        <v>0.97309999999999997</v>
+        <v>0.94540000000000002</v>
       </c>
       <c r="F20" s="4">
-        <v>0.94540000000000002</v>
+        <v>0.94589999999999996</v>
       </c>
       <c r="G20" s="4">
-        <v>0.94589999999999996</v>
+        <v>0.87719999999999998</v>
       </c>
       <c r="H20" s="4">
-        <v>0.87719999999999998</v>
+        <v>0.89290000000000003</v>
       </c>
       <c r="I20" s="4">
-        <v>0.89290000000000003</v>
+        <v>0.94040000000000001</v>
       </c>
       <c r="J20" s="4">
-        <v>0.94040000000000001</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>26</v>
+        <v>0.97660000000000002</v>
       </c>
       <c r="E21" s="4">
-        <v>0.97660000000000002</v>
+        <v>0.92979999999999996</v>
       </c>
       <c r="F21" s="4">
-        <v>0.92979999999999996</v>
+        <v>0.93059999999999998</v>
       </c>
       <c r="G21" s="4">
-        <v>0.93059999999999998</v>
+        <v>0.85450000000000004</v>
       </c>
       <c r="H21" s="4">
-        <v>0.85450000000000004</v>
+        <v>0.83930000000000005</v>
       </c>
       <c r="I21" s="4">
-        <v>0.83930000000000005</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="J21" s="4">
-        <v>0.92200000000000004</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.8468</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>19</v>
+        <v>0.97389999999999999</v>
       </c>
       <c r="E22" s="4">
-        <v>0.97389999999999999</v>
+        <v>0.9214</v>
       </c>
       <c r="F22" s="4">
-        <v>0.9214</v>
+        <v>0.92330000000000001</v>
       </c>
       <c r="G22" s="4">
-        <v>0.92330000000000001</v>
+        <v>0.90739999999999998</v>
       </c>
       <c r="H22" s="4">
-        <v>0.90739999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="I22" s="4">
-        <v>0.875</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="J22" s="4">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.89090000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>30</v>
+        <v>0.96809999999999996</v>
       </c>
       <c r="E23" s="4">
-        <v>0.96809999999999996</v>
+        <v>0.91949999999999998</v>
       </c>
       <c r="F23" s="4">
-        <v>0.91949999999999998</v>
+        <v>0.9204</v>
       </c>
       <c r="G23" s="4">
-        <v>0.9204</v>
+        <v>0.89580000000000004</v>
       </c>
       <c r="H23" s="4">
-        <v>0.89580000000000004</v>
+        <v>0.76790000000000003</v>
       </c>
       <c r="I23" s="4">
-        <v>0.76790000000000003</v>
+        <v>0.91739999999999999</v>
       </c>
       <c r="J23" s="4">
-        <v>0.91739999999999999</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.82689999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>24</v>
+        <v>0.98080000000000001</v>
       </c>
       <c r="E24" s="4">
-        <v>0.98080000000000001</v>
+        <v>0.96650000000000003</v>
       </c>
       <c r="F24" s="4">
-        <v>0.96650000000000003</v>
+        <v>0.96679999999999999</v>
       </c>
       <c r="G24" s="4">
-        <v>0.96679999999999999</v>
+        <v>0.84619999999999995</v>
       </c>
       <c r="H24" s="4">
-        <v>0.84619999999999995</v>
+        <v>0.98209999999999997</v>
       </c>
       <c r="I24" s="4">
-        <v>0.98209999999999997</v>
+        <v>0.94950000000000001</v>
       </c>
       <c r="J24" s="4">
-        <v>0.94950000000000001</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9745±0.0047</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9745±0.0047</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9365±0.0196</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9365±0.0196</v>
+        <f t="shared" si="3"/>
+        <v>0.9374±0.0192</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9374±0.0192</v>
+        <v>0.8762±0.0261</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8762±0.0261</v>
+        <v>0.8714±0.0782</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8714±0.0782</v>
+        <v>0.9349±0.0143</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9349±0.0143</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.8717±0.0338</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>30</v>
+        <v>0.98</v>
       </c>
       <c r="E26" s="4">
-        <v>0.98</v>
+        <v>0.98670000000000002</v>
       </c>
       <c r="F26" s="4">
         <v>0.98670000000000002</v>
       </c>
       <c r="G26" s="4">
-        <v>0.98670000000000002</v>
+        <v>0.93469999999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>0.93469999999999998</v>
+        <v>0.95879999999999999</v>
       </c>
       <c r="I26" s="4">
-        <v>0.95879999999999999</v>
+        <v>0.93379999999999996</v>
       </c>
       <c r="J26" s="4">
-        <v>0.93379999999999996</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.9466</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>30</v>
+        <v>0.98909999999999998</v>
       </c>
       <c r="E27" s="4">
-        <v>0.98909999999999998</v>
+        <v>0.9929</v>
       </c>
       <c r="F27" s="4">
         <v>0.9929</v>
       </c>
       <c r="G27" s="4">
-        <v>0.9929</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="H27" s="4">
-        <v>0.95899999999999996</v>
+        <v>0.96389999999999998</v>
       </c>
       <c r="I27" s="4">
-        <v>0.96389999999999998</v>
+        <v>0.95269999999999999</v>
       </c>
       <c r="J27" s="4">
-        <v>0.95269999999999999</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.96140000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>30</v>
+        <v>0.98040000000000005</v>
       </c>
       <c r="E28" s="4">
-        <v>0.98040000000000005</v>
+        <v>0.98570000000000002</v>
       </c>
       <c r="F28" s="4">
         <v>0.98570000000000002</v>
       </c>
       <c r="G28" s="4">
-        <v>0.98570000000000002</v>
+        <v>0.92649999999999999</v>
       </c>
       <c r="H28" s="4">
-        <v>0.92649999999999999</v>
+        <v>0.97419999999999995</v>
       </c>
       <c r="I28" s="4">
-        <v>0.97419999999999995</v>
+        <v>0.93689999999999996</v>
       </c>
       <c r="J28" s="4">
-        <v>0.93689999999999996</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.94969999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>25</v>
+        <v>0.98070000000000002</v>
       </c>
       <c r="E29" s="4">
-        <v>0.98070000000000002</v>
+        <v>0.98719999999999997</v>
       </c>
       <c r="F29" s="4">
         <v>0.98719999999999997</v>
       </c>
       <c r="G29" s="4">
-        <v>0.98719999999999997</v>
+        <v>0.92569999999999997</v>
       </c>
       <c r="H29" s="4">
-        <v>0.92569999999999997</v>
+        <v>0.96389999999999998</v>
       </c>
       <c r="I29" s="4">
-        <v>0.96389999999999998</v>
+        <v>0.93059999999999998</v>
       </c>
       <c r="J29" s="4">
-        <v>0.93059999999999998</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.94440000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>22</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="E30" s="4">
-        <v>0.98299999999999998</v>
+        <v>0.9889</v>
       </c>
       <c r="F30" s="4">
-        <v>0.9889</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="G30" s="4">
-        <v>0.98899999999999999</v>
+        <v>0.94389999999999996</v>
       </c>
       <c r="H30" s="4">
-        <v>0.94389999999999996</v>
+        <v>0.9536</v>
       </c>
       <c r="I30" s="4">
-        <v>0.9536</v>
+        <v>0.93689999999999996</v>
       </c>
       <c r="J30" s="4">
-        <v>0.93689999999999996</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.94869999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9826±0.0038</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9826±0.0038</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9883±0.0028</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
+        <f t="shared" si="4"/>
         <v>0.9883±0.0028</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9883±0.0028</v>
+        <v>0.9380±0.0139</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9380±0.0139</v>
+        <v>0.9629±0.0076</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9629±0.0076</v>
+        <v>0.9382±0.0085</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9382±0.0085</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9502±0.0066</v>
       </c>
@@ -3666,9 +3499,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA5AEE6-AEDC-49AA-B1CC-464D1D19E892}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3699,1072 +3532,990 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
+        <v>0.90549999999999997</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.88480000000000003</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.88529999999999998</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.79469999999999996</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.86580000000000001</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.83</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.82869999999999999</v>
+      </c>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4">
-        <v>0.90549999999999997</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.88480000000000003</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.88529999999999998</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0.79469999999999996</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0.86580000000000001</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0.83</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0.82869999999999999</v>
-      </c>
-      <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>13</v>
+        <v>0.878</v>
       </c>
       <c r="E3" s="4">
-        <v>0.878</v>
+        <v>0.84509999999999996</v>
       </c>
       <c r="F3" s="4">
-        <v>0.84509999999999996</v>
+        <v>0.84550000000000003</v>
       </c>
       <c r="G3" s="4">
-        <v>0.84550000000000003</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="H3" s="4">
-        <v>0.80800000000000005</v>
+        <v>0.74209999999999998</v>
       </c>
       <c r="I3" s="4">
-        <v>0.74209999999999998</v>
+        <v>0.79369999999999996</v>
       </c>
       <c r="J3" s="4">
-        <v>0.79369999999999996</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.77370000000000005</v>
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>13</v>
+        <v>0.8931</v>
       </c>
       <c r="E4" s="4">
-        <v>0.8931</v>
+        <v>0.87290000000000001</v>
       </c>
       <c r="F4" s="4">
-        <v>0.87290000000000001</v>
+        <v>0.87329999999999997</v>
       </c>
       <c r="G4" s="4">
-        <v>0.87329999999999997</v>
+        <v>0.77859999999999996</v>
       </c>
       <c r="H4" s="4">
-        <v>0.77859999999999996</v>
+        <v>0.84209999999999996</v>
       </c>
       <c r="I4" s="4">
-        <v>0.84209999999999996</v>
+        <v>0.81130000000000002</v>
       </c>
       <c r="J4" s="4">
-        <v>0.81130000000000002</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.80910000000000004</v>
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>25</v>
+        <v>0.87480000000000002</v>
       </c>
       <c r="E5" s="4">
-        <v>0.87480000000000002</v>
+        <v>0.86529999999999996</v>
       </c>
       <c r="F5" s="4">
-        <v>0.86529999999999996</v>
+        <v>0.86560000000000004</v>
       </c>
       <c r="G5" s="4">
-        <v>0.86560000000000004</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="H5" s="4">
-        <v>0.75600000000000001</v>
+        <v>0.83160000000000001</v>
       </c>
       <c r="I5" s="4">
-        <v>0.83160000000000001</v>
+        <v>0.79249999999999998</v>
       </c>
       <c r="J5" s="4">
-        <v>0.79249999999999998</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.79200000000000004</v>
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>28</v>
+        <v>0.89610000000000001</v>
       </c>
       <c r="E6" s="4">
-        <v>0.89610000000000001</v>
+        <v>0.8821</v>
       </c>
       <c r="F6" s="4">
-        <v>0.8821</v>
+        <v>0.88229999999999997</v>
       </c>
       <c r="G6" s="4">
-        <v>0.88229999999999997</v>
+        <v>0.80410000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>0.80410000000000004</v>
+        <v>0.82110000000000005</v>
       </c>
       <c r="I6" s="4">
-        <v>0.82110000000000005</v>
+        <v>0.82</v>
       </c>
       <c r="J6" s="4">
-        <v>0.82</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.8125</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.8895±0.0129</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.8895±0.0129</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.8700±0.0159</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.8700±0.0159</v>
+        <f t="shared" si="0"/>
+        <v>0.8704±0.0159</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8704±0.0159</v>
+        <v>0.7883±0.0213</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.7883±0.0213</v>
+        <v>0.8205±0.0469</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8205±0.0469</v>
+        <v>0.8095±0.0164</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8095±0.0164</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8032±0.0210</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>27</v>
+        <v>0.87239999999999995</v>
       </c>
       <c r="E8" s="4">
-        <v>0.87239999999999995</v>
+        <v>0.87890000000000001</v>
       </c>
       <c r="F8" s="4">
-        <v>0.87890000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="G8" s="4">
-        <v>0.879</v>
+        <v>0.74550000000000005</v>
       </c>
       <c r="H8" s="4">
-        <v>0.74550000000000005</v>
+        <v>0.83789999999999998</v>
       </c>
       <c r="I8" s="4">
-        <v>0.83789999999999998</v>
+        <v>0.77759999999999996</v>
       </c>
       <c r="J8" s="4">
-        <v>0.77759999999999996</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.78900000000000003</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>11</v>
+        <v>0.85519999999999996</v>
       </c>
       <c r="E9" s="4">
-        <v>0.85519999999999996</v>
+        <v>0.85609999999999997</v>
       </c>
       <c r="F9" s="4">
-        <v>0.85609999999999997</v>
+        <v>0.85619999999999996</v>
       </c>
       <c r="G9" s="4">
-        <v>0.85619999999999996</v>
+        <v>0.78690000000000004</v>
       </c>
       <c r="H9" s="4">
-        <v>0.78690000000000004</v>
+        <v>0.75690000000000002</v>
       </c>
       <c r="I9" s="4">
-        <v>0.75690000000000002</v>
+        <v>0.77759999999999996</v>
       </c>
       <c r="J9" s="4">
-        <v>0.77759999999999996</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.77159999999999995</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
+        <v>0.86050000000000004</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.86009999999999998</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.86050000000000004</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.76959999999999995</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.80810000000000004</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.78469999999999995</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.78839999999999999</v>
+      </c>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="4">
-        <v>0.86050000000000004</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0.86009999999999998</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.86050000000000004</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.76959999999999995</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0.80810000000000004</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0.78469999999999995</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0.78839999999999999</v>
-      </c>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>29</v>
+        <v>0.85340000000000005</v>
       </c>
       <c r="E11" s="4">
-        <v>0.85340000000000005</v>
+        <v>0.86050000000000004</v>
       </c>
       <c r="F11" s="4">
-        <v>0.86050000000000004</v>
+        <v>0.86060000000000003</v>
       </c>
       <c r="G11" s="4">
-        <v>0.86060000000000003</v>
+        <v>0.76390000000000002</v>
       </c>
       <c r="H11" s="4">
-        <v>0.76390000000000002</v>
+        <v>0.78669999999999995</v>
       </c>
       <c r="I11" s="4">
-        <v>0.78669999999999995</v>
+        <v>0.77349999999999997</v>
       </c>
       <c r="J11" s="4">
-        <v>0.77349999999999997</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.77510000000000001</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>28</v>
+        <v>0.86829999999999996</v>
       </c>
       <c r="E12" s="4">
-        <v>0.86829999999999996</v>
+        <v>0.87129999999999996</v>
       </c>
       <c r="F12" s="4">
-        <v>0.87129999999999996</v>
+        <v>0.87139999999999995</v>
       </c>
       <c r="G12" s="4">
-        <v>0.87139999999999995</v>
+        <v>0.77739999999999998</v>
       </c>
       <c r="H12" s="4">
-        <v>0.77739999999999998</v>
+        <v>0.81169999999999998</v>
       </c>
       <c r="I12" s="4">
-        <v>0.81169999999999998</v>
+        <v>0.79120000000000001</v>
       </c>
       <c r="J12" s="4">
-        <v>0.79120000000000001</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.79420000000000002</v>
       </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.8620±0.0082</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.8620±0.0082</v>
+        <f t="shared" si="1"/>
+        <v>0.8654±0.0094</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8654±0.0094</v>
+        <v>0.8655±0.0094</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8655±0.0094</v>
+        <v>0.7687±0.0156</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7687±0.0156</v>
+        <v>0.8003±0.0303</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8003±0.0303</v>
+        <v>0.7809±0.0070</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7809±0.0070</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.7837±0.0098</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>7</v>
+        <v>0.74250000000000005</v>
       </c>
       <c r="E14" s="4">
-        <v>0.74250000000000005</v>
+        <v>0.78690000000000004</v>
       </c>
       <c r="F14" s="4">
-        <v>0.78690000000000004</v>
+        <v>0.7873</v>
       </c>
       <c r="G14" s="4">
-        <v>0.7873</v>
+        <v>0.69640000000000002</v>
       </c>
       <c r="H14" s="4">
-        <v>0.69640000000000002</v>
+        <v>0.78580000000000005</v>
       </c>
       <c r="I14" s="4">
-        <v>0.78580000000000005</v>
+        <v>0.67720000000000002</v>
       </c>
       <c r="J14" s="4">
-        <v>0.67720000000000002</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.73839999999999995</v>
       </c>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>3</v>
+        <v>0.73029999999999995</v>
       </c>
       <c r="E15" s="4">
-        <v>0.73029999999999995</v>
+        <v>0.77710000000000001</v>
       </c>
       <c r="F15" s="4">
-        <v>0.77710000000000001</v>
+        <v>0.77729999999999999</v>
       </c>
       <c r="G15" s="4">
-        <v>0.77729999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H15" s="4">
-        <v>0.75</v>
+        <v>0.69889999999999997</v>
       </c>
       <c r="I15" s="4">
-        <v>0.69889999999999997</v>
+        <v>0.69030000000000002</v>
       </c>
       <c r="J15" s="4">
-        <v>0.69030000000000002</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.72360000000000002</v>
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>8</v>
+        <v>0.72589999999999999</v>
       </c>
       <c r="E16" s="4">
-        <v>0.72589999999999999</v>
+        <v>0.76029999999999998</v>
       </c>
       <c r="F16" s="4">
-        <v>0.76029999999999998</v>
+        <v>0.76090000000000002</v>
       </c>
       <c r="G16" s="4">
-        <v>0.76090000000000002</v>
+        <v>0.70540000000000003</v>
       </c>
       <c r="H16" s="4">
-        <v>0.70540000000000003</v>
+        <v>0.7611</v>
       </c>
       <c r="I16" s="4">
-        <v>0.7611</v>
+        <v>0.67720000000000002</v>
       </c>
       <c r="J16" s="4">
-        <v>0.67720000000000002</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.73219999999999996</v>
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>5</v>
+        <v>0.72660000000000002</v>
       </c>
       <c r="E17" s="4">
-        <v>0.72660000000000002</v>
+        <v>0.76619999999999999</v>
       </c>
       <c r="F17" s="4">
-        <v>0.76619999999999999</v>
+        <v>0.76670000000000005</v>
       </c>
       <c r="G17" s="4">
-        <v>0.76670000000000005</v>
+        <v>0.70350000000000001</v>
       </c>
       <c r="H17" s="4">
-        <v>0.70350000000000001</v>
+        <v>0.72850000000000004</v>
       </c>
       <c r="I17" s="4">
-        <v>0.72850000000000004</v>
+        <v>0.66459999999999997</v>
       </c>
       <c r="J17" s="4">
-        <v>0.66459999999999997</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.71579999999999999</v>
       </c>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>1</v>
+        <v>0.74109999999999998</v>
       </c>
       <c r="E18" s="4">
-        <v>0.74109999999999998</v>
+        <v>0.79620000000000002</v>
       </c>
       <c r="F18" s="4">
-        <v>0.79620000000000002</v>
+        <v>0.7964</v>
       </c>
       <c r="G18" s="4">
-        <v>0.7964</v>
+        <v>0.84489999999999998</v>
       </c>
       <c r="H18" s="4">
-        <v>0.84489999999999998</v>
+        <v>0.2636</v>
       </c>
       <c r="I18" s="4">
-        <v>0.2636</v>
+        <v>0.54490000000000005</v>
       </c>
       <c r="J18" s="4">
-        <v>0.54490000000000005</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.40179999999999999</v>
       </c>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7333±0.0080</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7333±0.0080</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7773±0.0147</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7773±0.0147</v>
+        <f t="shared" si="2"/>
+        <v>0.7777±0.0145</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7777±0.0145</v>
+        <v>0.7400±0.0623</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7400±0.0623</v>
+        <v>0.6476±0.2171</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6476±0.2171</v>
+        <v>0.6508±0.0599</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6508±0.0599</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.6624±0.1459</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>16</v>
+        <v>0.88149999999999995</v>
       </c>
       <c r="E20" s="4">
-        <v>0.88149999999999995</v>
+        <v>0.87339999999999995</v>
       </c>
       <c r="F20" s="4">
-        <v>0.87339999999999995</v>
+        <v>0.87390000000000001</v>
       </c>
       <c r="G20" s="4">
-        <v>0.87390000000000001</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="H20" s="4">
-        <v>0.84499999999999997</v>
+        <v>0.73650000000000004</v>
       </c>
       <c r="I20" s="4">
-        <v>0.73650000000000004</v>
+        <v>0.82850000000000001</v>
       </c>
       <c r="J20" s="4">
-        <v>0.82850000000000001</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.78700000000000003</v>
       </c>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>23</v>
+        <v>0.88160000000000005</v>
       </c>
       <c r="E21" s="4">
-        <v>0.88160000000000005</v>
+        <v>0.8639</v>
       </c>
       <c r="F21" s="4">
-        <v>0.8639</v>
+        <v>0.86450000000000005</v>
       </c>
       <c r="G21" s="4">
-        <v>0.86450000000000005</v>
+        <v>0.75639999999999996</v>
       </c>
       <c r="H21" s="4">
-        <v>0.75639999999999996</v>
+        <v>0.79730000000000001</v>
       </c>
       <c r="I21" s="4">
-        <v>0.79730000000000001</v>
+        <v>0.80230000000000001</v>
       </c>
       <c r="J21" s="4">
-        <v>0.80230000000000001</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.77629999999999999</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>20</v>
+        <v>0.86140000000000005</v>
       </c>
       <c r="E22" s="4">
-        <v>0.86140000000000005</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="F22" s="4">
-        <v>0.84199999999999997</v>
+        <v>0.84279999999999999</v>
       </c>
       <c r="G22" s="4">
-        <v>0.84279999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H22" s="4">
-        <v>0.75</v>
+        <v>0.79049999999999998</v>
       </c>
       <c r="I22" s="4">
-        <v>0.79049999999999998</v>
+        <v>0.79649999999999999</v>
       </c>
       <c r="J22" s="4">
-        <v>0.79649999999999999</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.76970000000000005</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>19</v>
+        <v>0.85189999999999999</v>
       </c>
       <c r="E23" s="4">
-        <v>0.85189999999999999</v>
+        <v>0.81879999999999997</v>
       </c>
       <c r="F23" s="4">
-        <v>0.81879999999999997</v>
+        <v>0.81979999999999997</v>
       </c>
       <c r="G23" s="4">
-        <v>0.81979999999999997</v>
+        <v>0.74209999999999998</v>
       </c>
       <c r="H23" s="4">
-        <v>0.74209999999999998</v>
+        <v>0.79730000000000001</v>
       </c>
       <c r="I23" s="4">
-        <v>0.79730000000000001</v>
+        <v>0.79359999999999997</v>
       </c>
       <c r="J23" s="4">
-        <v>0.79359999999999997</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.76870000000000005</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>17</v>
+        <v>0.86519999999999997</v>
       </c>
       <c r="E24" s="4">
-        <v>0.86519999999999997</v>
+        <v>0.82989999999999997</v>
       </c>
       <c r="F24" s="4">
-        <v>0.82989999999999997</v>
+        <v>0.8337</v>
       </c>
       <c r="G24" s="4">
-        <v>0.8337</v>
+        <v>0.78869999999999996</v>
       </c>
       <c r="H24" s="4">
-        <v>0.78869999999999996</v>
+        <v>0.75680000000000003</v>
       </c>
       <c r="I24" s="4">
-        <v>0.75680000000000003</v>
+        <v>0.80810000000000004</v>
       </c>
       <c r="J24" s="4">
-        <v>0.80810000000000004</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.77239999999999998</v>
       </c>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.8683±0.0130</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.8683±0.0130</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.8456±0.0228</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.8456±0.0228</v>
+        <f t="shared" si="3"/>
+        <v>0.8469±0.0222</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8469±0.0222</v>
+        <v>0.7764±0.0422</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7764±0.0422</v>
+        <v>0.7757±0.0276</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7757±0.0276</v>
+        <v>0.8058±0.0139</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8058±0.0139</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.7748±0.0074</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>5</v>
+        <v>0.7913</v>
       </c>
       <c r="E26" s="4">
-        <v>0.7913</v>
+        <v>0.80530000000000002</v>
       </c>
       <c r="F26" s="4">
-        <v>0.80530000000000002</v>
+        <v>0.80649999999999999</v>
       </c>
       <c r="G26" s="4">
-        <v>0.80649999999999999</v>
+        <v>0.64159999999999995</v>
       </c>
       <c r="H26" s="4">
-        <v>0.64159999999999995</v>
+        <v>0.90980000000000005</v>
       </c>
       <c r="I26" s="4">
-        <v>0.90980000000000005</v>
+        <v>0.68530000000000002</v>
       </c>
       <c r="J26" s="4">
-        <v>0.68530000000000002</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.75249999999999995</v>
       </c>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>5</v>
+        <v>0.76449999999999996</v>
       </c>
       <c r="E27" s="4">
-        <v>0.76449999999999996</v>
+        <v>0.75360000000000005</v>
       </c>
       <c r="F27" s="4">
-        <v>0.75360000000000005</v>
+        <v>0.75539999999999996</v>
       </c>
       <c r="G27" s="4">
-        <v>0.75539999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="H27" s="4">
-        <v>0.7</v>
+        <v>0.80330000000000001</v>
       </c>
       <c r="I27" s="4">
-        <v>0.80330000000000001</v>
+        <v>0.71550000000000002</v>
       </c>
       <c r="J27" s="4">
-        <v>0.71550000000000002</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.74809999999999999</v>
       </c>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>11</v>
+        <v>0.74770000000000003</v>
       </c>
       <c r="E28" s="4">
-        <v>0.74770000000000003</v>
+        <v>0.71740000000000004</v>
       </c>
       <c r="F28" s="4">
-        <v>0.71740000000000004</v>
+        <v>0.72160000000000002</v>
       </c>
       <c r="G28" s="4">
-        <v>0.72160000000000002</v>
+        <v>0.6452</v>
       </c>
       <c r="H28" s="4">
-        <v>0.6452</v>
+        <v>0.81969999999999998</v>
       </c>
       <c r="I28" s="4">
-        <v>0.81969999999999998</v>
+        <v>0.66810000000000003</v>
       </c>
       <c r="J28" s="4">
-        <v>0.66810000000000003</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.72199999999999998</v>
       </c>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>27</v>
+        <v>0.74109999999999998</v>
       </c>
       <c r="E29" s="4">
-        <v>0.74109999999999998</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="F29" s="4">
-        <v>0.70099999999999996</v>
+        <v>0.7046</v>
       </c>
       <c r="G29" s="4">
-        <v>0.7046</v>
+        <v>0.66449999999999998</v>
       </c>
       <c r="H29" s="4">
-        <v>0.66449999999999998</v>
+        <v>0.84430000000000005</v>
       </c>
       <c r="I29" s="4">
-        <v>0.84430000000000005</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J29" s="4">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.74370000000000003</v>
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>4</v>
+        <v>0.75790000000000002</v>
       </c>
       <c r="E30" s="4">
-        <v>0.75790000000000002</v>
+        <v>0.78310000000000002</v>
       </c>
       <c r="F30" s="4">
-        <v>0.78310000000000002</v>
+        <v>0.7843</v>
       </c>
       <c r="G30" s="4">
-        <v>0.7843</v>
+        <v>0.64739999999999998</v>
       </c>
       <c r="H30" s="4">
-        <v>0.64739999999999998</v>
+        <v>0.82789999999999997</v>
       </c>
       <c r="I30" s="4">
-        <v>0.82789999999999997</v>
+        <v>0.6724</v>
       </c>
       <c r="J30" s="4">
-        <v>0.6724</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.72660000000000002</v>
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.7605±0.0194</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.7605±0.0194</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.7521±0.0436</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.7521±0.0436</v>
+        <f t="shared" si="4"/>
+        <v>0.7545±0.0423</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7545±0.0423</v>
+        <v>0.6597±0.0242</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.6597±0.0242</v>
+        <v>0.8410±0.0412</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8410±0.0412</v>
+        <v>0.6871±0.0189</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.6871±0.0189</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.7386±0.0135</v>
       </c>
@@ -4778,10 +4529,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45275180-57AC-4BB6-B1CC-6E162588BEA5}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4812,402 +4563,371 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>24</v>
+        <v>0.95930000000000004</v>
       </c>
       <c r="E2" s="4">
-        <v>0.95930000000000004</v>
+        <v>0.94810000000000005</v>
       </c>
       <c r="F2" s="4">
-        <v>0.94810000000000005</v>
+        <v>0.94830000000000003</v>
       </c>
       <c r="G2" s="4">
-        <v>0.94830000000000003</v>
+        <v>0.91039999999999999</v>
       </c>
       <c r="H2" s="4">
-        <v>0.91039999999999999</v>
+        <v>0.90590000000000004</v>
       </c>
       <c r="I2" s="4">
-        <v>0.90590000000000004</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="J2" s="4">
-        <v>0.91300000000000003</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.90820000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>13</v>
+        <v>0.94630000000000003</v>
       </c>
       <c r="E3" s="4">
-        <v>0.94630000000000003</v>
+        <v>0.93189999999999995</v>
       </c>
       <c r="F3" s="4">
-        <v>0.93189999999999995</v>
+        <v>0.93210000000000004</v>
       </c>
       <c r="G3" s="4">
-        <v>0.93210000000000004</v>
+        <v>0.87319999999999998</v>
       </c>
       <c r="H3" s="4">
-        <v>0.87319999999999998</v>
+        <v>0.90349999999999997</v>
       </c>
       <c r="I3" s="4">
-        <v>0.90349999999999997</v>
+        <v>0.89190000000000003</v>
       </c>
       <c r="J3" s="4">
-        <v>0.89190000000000003</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.8881</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>10</v>
+        <v>0.95169999999999999</v>
       </c>
       <c r="E4" s="4">
-        <v>0.95169999999999999</v>
+        <v>0.94420000000000004</v>
       </c>
       <c r="F4" s="4">
-        <v>0.94420000000000004</v>
+        <v>0.94430000000000003</v>
       </c>
       <c r="G4" s="4">
-        <v>0.94430000000000003</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="H4" s="4">
-        <v>0.84899999999999998</v>
+        <v>0.91830000000000001</v>
       </c>
       <c r="I4" s="4">
-        <v>0.91830000000000001</v>
+        <v>0.88370000000000004</v>
       </c>
       <c r="J4" s="4">
-        <v>0.88370000000000004</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.88229999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>12</v>
+        <v>0.93979999999999997</v>
       </c>
       <c r="E5" s="4">
-        <v>0.93979999999999997</v>
+        <v>0.92</v>
       </c>
       <c r="F5" s="4">
-        <v>0.92</v>
+        <v>0.92020000000000002</v>
       </c>
       <c r="G5" s="4">
-        <v>0.92020000000000002</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="H5" s="4">
-        <v>0.84899999999999998</v>
+        <v>0.91830000000000001</v>
       </c>
       <c r="I5" s="4">
-        <v>0.91830000000000001</v>
+        <v>0.88370000000000004</v>
       </c>
       <c r="J5" s="4">
-        <v>0.88370000000000004</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.88229999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>12</v>
+        <v>0.95550000000000002</v>
       </c>
       <c r="E6" s="4">
-        <v>0.95550000000000002</v>
+        <v>0.94850000000000001</v>
       </c>
       <c r="F6" s="4">
-        <v>0.94850000000000001</v>
+        <v>0.9486</v>
       </c>
       <c r="G6" s="4">
-        <v>0.9486</v>
+        <v>0.89190000000000003</v>
       </c>
       <c r="H6" s="4">
-        <v>0.89190000000000003</v>
+        <v>0.89849999999999997</v>
       </c>
       <c r="I6" s="4">
-        <v>0.89849999999999997</v>
+        <v>0.90010000000000001</v>
       </c>
       <c r="J6" s="4">
-        <v>0.90010000000000001</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.8952</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9505±0.0077</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9505±0.0077</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9385±0.0124</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.9385±0.0124</v>
+        <f t="shared" si="0"/>
+        <v>0.9387±0.0123</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9387±0.0123</v>
+        <v>0.8747±0.0269</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8747±0.0269</v>
+        <v>0.9089±0.0090</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9089±0.0090</v>
+        <v>0.8945±0.0124</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8945±0.0124</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8912±0.0109</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>24</v>
+        <v>0.94169999999999998</v>
       </c>
       <c r="E8" s="4">
-        <v>0.94169999999999998</v>
+        <v>0.93830000000000002</v>
       </c>
       <c r="F8" s="4">
-        <v>0.93830000000000002</v>
+        <v>0.93840000000000001</v>
       </c>
       <c r="G8" s="4">
-        <v>0.93840000000000001</v>
+        <v>0.86919999999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>0.86919999999999997</v>
+        <v>0.88419999999999999</v>
       </c>
       <c r="I8" s="4">
-        <v>0.88419999999999999</v>
+        <v>0.877</v>
       </c>
       <c r="J8" s="4">
-        <v>0.877</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.87660000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>22</v>
+        <v>0.9375</v>
       </c>
       <c r="E9" s="4">
-        <v>0.9375</v>
+        <v>0.93359999999999999</v>
       </c>
       <c r="F9" s="4">
-        <v>0.93359999999999999</v>
+        <v>0.93369999999999997</v>
       </c>
       <c r="G9" s="4">
-        <v>0.93369999999999997</v>
+        <v>0.85589999999999999</v>
       </c>
       <c r="H9" s="4">
-        <v>0.85589999999999999</v>
+        <v>0.88529999999999998</v>
       </c>
       <c r="I9" s="4">
-        <v>0.88529999999999998</v>
+        <v>0.86960000000000004</v>
       </c>
       <c r="J9" s="4">
-        <v>0.86960000000000004</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.87029999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>18</v>
+        <v>0.94510000000000005</v>
       </c>
       <c r="E10" s="4">
-        <v>0.94510000000000005</v>
+        <v>0.94259999999999999</v>
       </c>
       <c r="F10" s="4">
         <v>0.94259999999999999</v>
       </c>
       <c r="G10" s="4">
-        <v>0.94259999999999999</v>
+        <v>0.85370000000000001</v>
       </c>
       <c r="H10" s="4">
-        <v>0.85370000000000001</v>
+        <v>0.89680000000000004</v>
       </c>
       <c r="I10" s="4">
-        <v>0.89680000000000004</v>
+        <v>0.873</v>
       </c>
       <c r="J10" s="4">
-        <v>0.873</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.87470000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>25</v>
+        <v>0.9335</v>
       </c>
       <c r="E11" s="4">
-        <v>0.9335</v>
+        <v>0.92989999999999995</v>
       </c>
       <c r="F11" s="4">
         <v>0.92989999999999995</v>
       </c>
       <c r="G11" s="4">
-        <v>0.92989999999999995</v>
+        <v>0.81810000000000005</v>
       </c>
       <c r="H11" s="4">
-        <v>0.81810000000000005</v>
+        <v>0.91279999999999994</v>
       </c>
       <c r="I11" s="4">
-        <v>0.91279999999999994</v>
+        <v>0.85660000000000003</v>
       </c>
       <c r="J11" s="4">
-        <v>0.85660000000000003</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.8629</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>19</v>
+        <v>0.94110000000000005</v>
       </c>
       <c r="E12" s="4">
-        <v>0.94110000000000005</v>
+        <v>0.94240000000000002</v>
       </c>
       <c r="F12" s="4">
-        <v>0.94240000000000002</v>
+        <v>0.9425</v>
       </c>
       <c r="G12" s="4">
-        <v>0.9425</v>
+        <v>0.8488</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8488</v>
+        <v>0.90139999999999998</v>
       </c>
       <c r="I12" s="4">
-        <v>0.90139999999999998</v>
+        <v>0.87190000000000001</v>
       </c>
       <c r="J12" s="4">
-        <v>0.87190000000000001</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.87429999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9398±0.0044</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9398±0.0044</v>
+        <f t="shared" si="1"/>
+        <v>0.9374±0.0056</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
@@ -5215,644 +4935,593 @@
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9374±0.0056</v>
+        <v>0.8491±0.0189</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8491±0.0189</v>
+        <v>0.8961±0.0119</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8961±0.0119</v>
+        <v>0.8696±0.0078</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8696±0.0078</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8718±0.0055</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>6</v>
+        <v>0.78190000000000004</v>
       </c>
       <c r="E14" s="4">
-        <v>0.78190000000000004</v>
+        <v>0.81079999999999997</v>
       </c>
       <c r="F14" s="4">
-        <v>0.81079999999999997</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="G14" s="4">
-        <v>0.81100000000000005</v>
+        <v>0.64870000000000005</v>
       </c>
       <c r="H14" s="4">
-        <v>0.64870000000000005</v>
+        <v>0.8831</v>
       </c>
       <c r="I14" s="4">
-        <v>0.8831</v>
+        <v>0.67269999999999996</v>
       </c>
       <c r="J14" s="4">
-        <v>0.67269999999999996</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.748</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>7</v>
+        <v>0.74219999999999997</v>
       </c>
       <c r="E15" s="4">
-        <v>0.74219999999999997</v>
+        <v>0.76060000000000005</v>
       </c>
       <c r="F15" s="4">
-        <v>0.76060000000000005</v>
+        <v>0.76139999999999997</v>
       </c>
       <c r="G15" s="4">
-        <v>0.76139999999999997</v>
+        <v>0.63170000000000004</v>
       </c>
       <c r="H15" s="4">
-        <v>0.63170000000000004</v>
+        <v>0.87670000000000003</v>
       </c>
       <c r="I15" s="4">
-        <v>0.87670000000000003</v>
+        <v>0.65110000000000001</v>
       </c>
       <c r="J15" s="4">
-        <v>0.65110000000000001</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>8</v>
+        <v>0.72250000000000003</v>
       </c>
       <c r="E16" s="4">
-        <v>0.72250000000000003</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="F16" s="4">
-        <v>0.76100000000000001</v>
+        <v>0.76119999999999999</v>
       </c>
       <c r="G16" s="4">
-        <v>0.76119999999999999</v>
+        <v>0.63380000000000003</v>
       </c>
       <c r="H16" s="4">
-        <v>0.63380000000000003</v>
+        <v>0.84060000000000001</v>
       </c>
       <c r="I16" s="4">
-        <v>0.84060000000000001</v>
+        <v>0.6452</v>
       </c>
       <c r="J16" s="4">
-        <v>0.6452</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.72270000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>16</v>
+        <v>0.77849999999999997</v>
       </c>
       <c r="E17" s="4">
-        <v>0.77849999999999997</v>
+        <v>0.80069999999999997</v>
       </c>
       <c r="F17" s="4">
-        <v>0.80069999999999997</v>
+        <v>0.80089999999999995</v>
       </c>
       <c r="G17" s="4">
-        <v>0.80089999999999995</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="H17" s="4">
-        <v>0.66900000000000004</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="I17" s="4">
-        <v>0.89800000000000002</v>
+        <v>0.6996</v>
       </c>
       <c r="J17" s="4">
-        <v>0.6996</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.76680000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>13</v>
+        <v>0.79479999999999995</v>
       </c>
       <c r="E18" s="4">
-        <v>0.79479999999999995</v>
+        <v>0.83720000000000006</v>
       </c>
       <c r="F18" s="4">
-        <v>0.83720000000000006</v>
+        <v>0.83730000000000004</v>
       </c>
       <c r="G18" s="4">
-        <v>0.83730000000000004</v>
+        <v>0.65710000000000002</v>
       </c>
       <c r="H18" s="4">
-        <v>0.65710000000000002</v>
+        <v>0.9022</v>
       </c>
       <c r="I18" s="4">
-        <v>0.9022</v>
+        <v>0.68730000000000002</v>
       </c>
       <c r="J18" s="4">
-        <v>0.68730000000000002</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.76039999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7640±0.0303</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7640±0.0303</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7941±0.0332</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7941±0.0332</v>
+        <f t="shared" si="2"/>
+        <v>0.7944±0.0330</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7944±0.0330</v>
+        <v>0.6481±0.0157</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6481±0.0157</v>
+        <v>0.8801±0.0244</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8801±0.0244</v>
+        <v>0.6712±0.0232</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6712±0.0232</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.7464±0.0182</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>16</v>
+        <v>0.96619999999999995</v>
       </c>
       <c r="E20" s="4">
         <v>0.96619999999999995</v>
       </c>
       <c r="F20" s="4">
-        <v>0.96619999999999995</v>
+        <v>0.96630000000000005</v>
       </c>
       <c r="G20" s="4">
-        <v>0.96630000000000005</v>
+        <v>0.93059999999999998</v>
       </c>
       <c r="H20" s="4">
-        <v>0.93059999999999998</v>
+        <v>0.87770000000000004</v>
       </c>
       <c r="I20" s="4">
-        <v>0.87770000000000004</v>
+        <v>0.9073</v>
       </c>
       <c r="J20" s="4">
-        <v>0.9073</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.90339999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>23</v>
+        <v>0.95079999999999998</v>
       </c>
       <c r="E21" s="4">
-        <v>0.95079999999999998</v>
+        <v>0.94440000000000002</v>
       </c>
       <c r="F21" s="4">
-        <v>0.94440000000000002</v>
+        <v>0.94450000000000001</v>
       </c>
       <c r="G21" s="4">
-        <v>0.94450000000000001</v>
+        <v>0.86360000000000003</v>
       </c>
       <c r="H21" s="4">
-        <v>0.86360000000000003</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="I21" s="4">
-        <v>0.91269999999999996</v>
+        <v>0.88580000000000003</v>
       </c>
       <c r="J21" s="4">
-        <v>0.88580000000000003</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.88749999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>20</v>
+        <v>0.95779999999999998</v>
       </c>
       <c r="E22" s="4">
-        <v>0.95779999999999998</v>
+        <v>0.95620000000000005</v>
       </c>
       <c r="F22" s="4">
-        <v>0.95620000000000005</v>
+        <v>0.95630000000000004</v>
       </c>
       <c r="G22" s="4">
-        <v>0.95630000000000004</v>
+        <v>0.8851</v>
       </c>
       <c r="H22" s="4">
-        <v>0.8851</v>
+        <v>0.9083</v>
       </c>
       <c r="I22" s="4">
-        <v>0.9083</v>
+        <v>0.89659999999999995</v>
       </c>
       <c r="J22" s="4">
-        <v>0.89659999999999995</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.89649999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>12</v>
+        <v>0.9425</v>
       </c>
       <c r="E23" s="4">
-        <v>0.9425</v>
+        <v>0.94120000000000004</v>
       </c>
       <c r="F23" s="4">
-        <v>0.94120000000000004</v>
+        <v>0.94130000000000003</v>
       </c>
       <c r="G23" s="4">
-        <v>0.94130000000000003</v>
+        <v>0.82589999999999997</v>
       </c>
       <c r="H23" s="4">
-        <v>0.82589999999999997</v>
+        <v>0.89080000000000004</v>
       </c>
       <c r="I23" s="4">
-        <v>0.89080000000000004</v>
+        <v>0.85340000000000005</v>
       </c>
       <c r="J23" s="4">
-        <v>0.85340000000000005</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>13</v>
+        <v>0.95069999999999999</v>
       </c>
       <c r="E24" s="4">
-        <v>0.95069999999999999</v>
+        <v>0.95050000000000001</v>
       </c>
       <c r="F24" s="4">
-        <v>0.95050000000000001</v>
+        <v>0.9506</v>
       </c>
       <c r="G24" s="4">
-        <v>0.9506</v>
+        <v>0.82469999999999999</v>
       </c>
       <c r="H24" s="4">
-        <v>0.82469999999999999</v>
+        <v>0.90390000000000004</v>
       </c>
       <c r="I24" s="4">
-        <v>0.90390000000000004</v>
+        <v>0.85780000000000001</v>
       </c>
       <c r="J24" s="4">
-        <v>0.85780000000000001</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.86250000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9536±0.0089</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9536±0.0089</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9517±0.0099</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9517±0.0099</v>
+        <f t="shared" si="3"/>
+        <v>0.9518±0.0099</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9518±0.0099</v>
+        <v>0.8660±0.0443</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8660±0.0443</v>
+        <v>0.8987±0.0143</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8987±0.0143</v>
+        <v>0.8802±0.0237</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8802±0.0237</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.8814±0.0206</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>24</v>
+        <v>0.80389999999999995</v>
       </c>
       <c r="E26" s="4">
-        <v>0.80389999999999995</v>
+        <v>0.84179999999999999</v>
       </c>
       <c r="F26" s="4">
-        <v>0.84179999999999999</v>
+        <v>0.84370000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>0.84370000000000001</v>
+        <v>0.79590000000000005</v>
       </c>
       <c r="H26" s="4">
-        <v>0.79590000000000005</v>
+        <v>0.8125</v>
       </c>
       <c r="I26" s="4">
-        <v>0.8125</v>
+        <v>0.76249999999999996</v>
       </c>
       <c r="J26" s="4">
-        <v>0.76249999999999996</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.80410000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>4</v>
+        <v>0.82389999999999997</v>
       </c>
       <c r="E27" s="4">
-        <v>0.82389999999999997</v>
+        <v>0.84260000000000002</v>
       </c>
       <c r="F27" s="4">
-        <v>0.84260000000000002</v>
+        <v>0.84450000000000003</v>
       </c>
       <c r="G27" s="4">
-        <v>0.84450000000000003</v>
+        <v>0.79810000000000003</v>
       </c>
       <c r="H27" s="4">
-        <v>0.79810000000000003</v>
+        <v>0.86460000000000004</v>
       </c>
       <c r="I27" s="4">
-        <v>0.86460000000000004</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="J27" s="4">
-        <v>0.78749999999999998</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.83</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>5</v>
+        <v>0.85009999999999997</v>
       </c>
       <c r="E28" s="4">
-        <v>0.85009999999999997</v>
+        <v>0.8831</v>
       </c>
       <c r="F28" s="4">
-        <v>0.8831</v>
+        <v>0.8841</v>
       </c>
       <c r="G28" s="4">
-        <v>0.8841</v>
+        <v>0.81730000000000003</v>
       </c>
       <c r="H28" s="4">
-        <v>0.81730000000000003</v>
+        <v>0.88539999999999996</v>
       </c>
       <c r="I28" s="4">
-        <v>0.88539999999999996</v>
+        <v>0.8125</v>
       </c>
       <c r="J28" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>5</v>
+        <v>0.83140000000000003</v>
       </c>
       <c r="E29" s="4">
-        <v>0.83140000000000003</v>
+        <v>0.89649999999999996</v>
       </c>
       <c r="F29" s="4">
-        <v>0.89649999999999996</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="G29" s="4">
-        <v>0.89700000000000002</v>
+        <v>0.75</v>
       </c>
       <c r="H29" s="4">
-        <v>0.75</v>
+        <v>0.84379999999999999</v>
       </c>
       <c r="I29" s="4">
-        <v>0.84379999999999999</v>
+        <v>0.73750000000000004</v>
       </c>
       <c r="J29" s="4">
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.79410000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>5</v>
+        <v>0.78339999999999999</v>
       </c>
       <c r="E30" s="4">
-        <v>0.78339999999999999</v>
+        <v>0.85409999999999997</v>
       </c>
       <c r="F30" s="4">
-        <v>0.85409999999999997</v>
+        <v>0.85519999999999996</v>
       </c>
       <c r="G30" s="4">
-        <v>0.85519999999999996</v>
+        <v>0.78490000000000004</v>
       </c>
       <c r="H30" s="4">
-        <v>0.78490000000000004</v>
+        <v>0.76039999999999996</v>
       </c>
       <c r="I30" s="4">
-        <v>0.76039999999999996</v>
+        <v>0.73119999999999996</v>
       </c>
       <c r="J30" s="4">
-        <v>0.73119999999999996</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.77249999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.8185±0.0257</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.8185±0.0257</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.8636±0.0248</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.8636±0.0248</v>
+        <f t="shared" si="4"/>
+        <v>0.8649±0.0243</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8649±0.0243</v>
+        <v>0.7892±0.0248</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7892±0.0248</v>
+        <v>0.8333±0.0489</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8333±0.0489</v>
+        <v>0.7662±0.0341</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.7662±0.0341</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.8101±0.0304</v>
       </c>
